--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755ABFBA-2FF4-4162-A18C-641CC963306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F085B5-5895-45E9-A397-75C440C697CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1569,26 +1569,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="14">
+        <v>500</v>
+      </c>
+      <c r="C18" s="14">
+        <v>15</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F085B5-5895-45E9-A397-75C440C697CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F03CDC-EC1D-4C6B-8664-C7B6206839E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1615,26 +1615,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B19" s="14">
+        <v>620</v>
+      </c>
+      <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <v>80</v>
+      </c>
+      <c r="E19" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F03CDC-EC1D-4C6B-8664-C7B6206839E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1586264-B4AC-4A23-AB55-1E39364093DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1661,26 +1661,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B20" s="14">
+        <v>500</v>
+      </c>
+      <c r="C20" s="14">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14">
+        <v>30</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>40</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>830</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1586264-B4AC-4A23-AB55-1E39364093DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7125057D-9C15-4981-A014-E7A51DB30CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1707,26 +1710,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B21" s="14">
+        <v>530</v>
+      </c>
+      <c r="C21" s="14">
+        <v>15</v>
+      </c>
+      <c r="D21" s="14">
+        <v>30</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7125057D-9C15-4981-A014-E7A51DB30CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1062EFE-6067-4CD4-9975-BB2CC381A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1756,26 +1756,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B22" s="14">
+        <v>740</v>
+      </c>
+      <c r="C22" s="14">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>50</v>
+      </c>
+      <c r="E22" s="14">
+        <v>40</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1062EFE-6067-4CD4-9975-BB2CC381A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EF2525-EB7F-4068-878A-DF83D7B9E7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1802,26 +1802,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B23" s="14">
+        <v>630</v>
+      </c>
+      <c r="C23" s="14">
+        <v>10</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EF2525-EB7F-4068-878A-DF83D7B9E7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A13CEF-980E-47C3-A102-C23EC8F3841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1848,26 +1848,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B24" s="14">
+        <v>600</v>
+      </c>
+      <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
+        <v>250</v>
+      </c>
+      <c r="E24" s="14">
+        <v>50</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>10</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A13CEF-980E-47C3-A102-C23EC8F3841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD53F4E-3E1D-40EB-8FB3-3737A66EFC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1894,26 +1894,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B25" s="14">
+        <v>600</v>
+      </c>
+      <c r="C25" s="14">
+        <v>15</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1315</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>125</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD53F4E-3E1D-40EB-8FB3-3737A66EFC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E68D13-90BE-4680-8ECE-AEFDC8FD276A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1940,26 +1940,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>300</v>
+      </c>
+      <c r="E26" s="14">
+        <v>200</v>
+      </c>
+      <c r="F26" s="14">
+        <v>150</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14">
+        <v>10</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E68D13-90BE-4680-8ECE-AEFDC8FD276A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C831DF6C-CDF1-4042-9103-043C62F293BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1986,26 +1986,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B27" s="14">
+        <v>600</v>
+      </c>
+      <c r="C27" s="14">
+        <v>15</v>
+      </c>
+      <c r="D27" s="14">
+        <v>100</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C831DF6C-CDF1-4042-9103-043C62F293BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB1965-2DA9-4195-9435-92AEF611222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2032,26 +2032,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B28" s="14">
+        <v>600</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>50</v>
+      </c>
+      <c r="E28" s="14">
+        <v>20</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB1965-2DA9-4195-9435-92AEF611222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE96F516-E84D-4A47-BE72-A74703B2CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2078,26 +2078,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B29" s="14">
+        <v>630</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>250</v>
+      </c>
+      <c r="E29" s="14">
+        <v>200</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>200</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE96F516-E84D-4A47-BE72-A74703B2CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C415888B-8742-4A5D-95D2-EFDD4FD13FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2124,26 +2124,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B30" s="14">
+        <v>700</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>50</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C415888B-8742-4A5D-95D2-EFDD4FD13FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB147C-AAB0-4054-A041-F9CE7D052489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2170,26 +2170,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B31" s="14">
+        <v>600</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>40</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>10</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB147C-AAB0-4054-A041-F9CE7D052489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F5E35C-9A90-4499-B70A-949E5DDEB3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B30" s="14">
         <v>700</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B31" s="14">
         <v>600</v>
@@ -2216,26 +2216,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B32" s="14">
+        <v>600</v>
+      </c>
+      <c r="C32" s="14">
+        <v>25</v>
+      </c>
+      <c r="D32" s="14">
+        <v>59</v>
+      </c>
+      <c r="E32" s="14">
+        <v>100</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>15</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1099</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>341</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
